--- a/Sprint-3/Ticket_Enable_Public_Browsing_Mode/Enable_Public_Browsing_Mode_Test_Cases.xlsx
+++ b/Sprint-3/Ticket_Enable_Public_Browsing_Mode/Enable_Public_Browsing_Mode_Test_Cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -464,7 +464,7 @@
         <v>User accesses mcstaging2.globewest.com as an unauthenticated guest.</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com/indoor
+        <v xml:space="preserve">Step 1: Navigate to https://mcstaging2.globewest.com/indoor
 2. Inspect top utility bar and header elements
 3. Verify presence of 'Become a Trade Customer' and 'Book Showroom'
 4. Verify Pricing Toggle visibility.</v>
@@ -502,7 +502,7 @@
         <v>User navigates to category PLP /indoor as guest.</v>
       </c>
       <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load https://mcstaging2.globewest.com/indoor
+        <v xml:space="preserve">Step 1: Load https://mcstaging2.globewest.com/indoor
 2. Inspect rendered product cards (48 items)
 3. Check DOM and computed text for '$' dollar signs or wholesale numbers.</v>
       </c>
@@ -539,7 +539,7 @@
         <v>User views product cards on PLP.</v>
       </c>
       <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect each product card for 'Add to Cart' button (.action.tocart)
+        <v xml:space="preserve">Step 1: Inspect each product card for 'Add to Cart' button (.action.tocart)
 2. Verify hover overlay actions.</v>
       </c>
       <c r="G4" t="str">
@@ -575,7 +575,7 @@
         <v>User views category header banner on /indoor.</v>
       </c>
       <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect category title and description copy
+        <v xml:space="preserve">Step 1: Inspect category title and description copy
 2. Verify absence of 'Australian homes' or domestic references.</v>
       </c>
       <c r="G5" t="str">
@@ -611,7 +611,7 @@
         <v>Inspect product image sources on /indoor.</v>
       </c>
       <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect img src attributes across PLP cards
+        <v xml:space="preserve">Step 1: Inspect img src attributes across PLP cards
 2. Enforce AGENTS.md Rule 4 (Zero Placeholders).</v>
       </c>
       <c r="G6" t="str">
@@ -647,7 +647,7 @@
         <v>User opens product PDP /base-2-seater-left-arm-sofa-oatmeal-light-oak-sof-ske-bas2s-lft-oat-lo.</v>
       </c>
       <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Verify product title, image gallery, specifications load
+        <v xml:space="preserve">Step 1: Verify product title, image gallery, specifications load
 2. Inspect price container (.product-info-price, .price-box).</v>
       </c>
       <c r="G7" t="str">
@@ -683,7 +683,7 @@
         <v>User views purchasing actions on PDP.</v>
       </c>
       <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect DOM for #product-addtocart-button
+        <v xml:space="preserve">Step 1: Inspect DOM for #product-addtocart-button
 2. Verify visibility and display style.</v>
       </c>
       <c r="G8" t="str">
@@ -719,7 +719,7 @@
         <v>Inspect PDP callout section below product title.</v>
       </c>
       <c r="F9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Verify presence of trade guidance CTA ('Become a Trade Customer' or 'Login for Trade Pricing')
+        <v xml:space="preserve">Step 1: Verify presence of trade guidance CTA ('Become a Trade Customer' or 'Login for Trade Pricing')
 2. Verify swatches request button.</v>
       </c>
       <c r="G9" t="str">
@@ -755,7 +755,7 @@
         <v>User enters search query in search bar (?q=chair).</v>
       </c>
       <c r="F10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com/catalogsearch/result/?q=chair
+        <v xml:space="preserve">Step 1: Navigate to https://mcstaging2.globewest.com/catalogsearch/result/?q=chair
 2. Verify rendered search results and price masking.</v>
       </c>
       <c r="G10" t="str">
@@ -791,7 +791,7 @@
         <v>Guest navigates directly to /checkout/cart/.</v>
       </c>
       <c r="F11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com/checkout/cart/
+        <v xml:space="preserve">Step 1: Navigate to https://mcstaging2.globewest.com/checkout/cart/
 2. Verify page behavior and checkout CTA state.</v>
       </c>
       <c r="G11" t="str">
@@ -827,7 +827,7 @@
         <v>User visits AU storefront (https://mcstaging2.globewest.com.au or live www.globewest.com.au).</v>
       </c>
       <c r="F12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to AU /indoor
+        <v xml:space="preserve">Step 1: Navigate to AU /indoor
 2. Open AU PDP
 3. Verify retail prices in AUD and Add to Cart button.</v>
       </c>
@@ -861,10 +861,10 @@
         <v>Verify Trade Transformation &amp; Price Toggle Activation Upon Login</v>
       </c>
       <c r="E13" t="str">
-        <v>User logs in with US Trade credentials (deepali.londhe@overdose.digital).</v>
+        <v>User logs in with US Trade credentials (trade.tester@globewest.com).</v>
       </c>
       <c r="F13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Authenticate via /customer/account/login/
+        <v xml:space="preserve">Step 1: Authenticate via /customer/account/login/
 2. Navigate to /indoor
 3. Verify Pricing Toggle and product card wholesale prices.</v>
       </c>
@@ -901,7 +901,7 @@
         <v>Logged-in Trade Customer on PLP/PDP.</v>
       </c>
       <c r="F14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click Trade pricing toggle in header
+        <v xml:space="preserve">Step 1: Click Trade pricing toggle in header
 2. Switch from 'Trade' to 'MSRP'
 3. Verify product card pricing updates dynamically.</v>
       </c>
@@ -938,7 +938,7 @@
         <v>Mobile viewport set to 393x852 (iPhone 16 / Pixel 5).</v>
       </c>
       <c r="F15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /indoor and PDP on mobile
+        <v xml:space="preserve">Step 1: Navigate to /indoor and PDP on mobile
 2. Verify single-column card stacking and price masking.</v>
       </c>
       <c r="G15" t="str">
@@ -974,7 +974,7 @@
         <v>Run accessibility inspection on public browsing pages.</v>
       </c>
       <c r="F16" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect hidden price elements for aria-hidden or display: none
+        <v xml:space="preserve">Step 1: Inspect hidden price elements for aria-hidden or display: none
 2. Verify screen reader does not announce suppressed prices.</v>
       </c>
       <c r="G16" t="str">
@@ -1010,7 +1010,7 @@
         <v>Logged-in Trade customer views product PDP with active lead time.</v>
       </c>
       <c r="F17" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to product PDP as trade customer
+        <v xml:space="preserve">Step 1: Navigate to product PDP as trade customer
 2. Inspect stock indicator below Add to Cart / Add to Quote
 3. Verify presence of available quantity in brackets e.g. 'ETA 14 Mar 2027 (8 available)'.</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>Logged-in Trade customer views product PDP with purchase order arriving in NetSuite.</v>
       </c>
       <c r="F18" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect second line under primary ETA status
+        <v xml:space="preserve">Step 1: Inspect second line under primary ETA status
 2. Check for next incoming PO shipment date and quantity e.g. 'Next Shipment: 8 (ETA 14 Mar 2027)'.</v>
       </c>
       <c r="G18" t="str">
@@ -1083,7 +1083,7 @@
         <v>User views product with ETA or Enquire for ETA status.</v>
       </c>
       <c r="F19" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect right side of ETA status indicator
+        <v xml:space="preserve">Step 1: Inspect right side of ETA status indicator
 2. Verify presence and interactivity of 'Notify me' alert trigger.</v>
       </c>
       <c r="G19" t="str">
@@ -1119,7 +1119,7 @@
         <v>Unauthenticated guest browses /indoor category PLP.</v>
       </c>
       <c r="F20" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /indoor as guest
+        <v xml:space="preserve">Step 1: Navigate to /indoor as guest
 2. Inspect product cards for inventory quantities or stock indicators.</v>
       </c>
       <c r="G20" t="str">
@@ -1138,9 +1138,84 @@
         <v>screenshots/02_US_PLP_GUEST_GRID.png</v>
       </c>
     </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-GW-PUB-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Header &amp; PLP / PDP CTAs</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Logged Out (Public Guest)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Verify 'Become a Trade Customer' CTA Redirection to Trade Registration Page</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Unauthenticated guest browsing storefront header or unpriced product page.</v>
+      </c>
+      <c r="F21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Click 'Become a Trade Customer' link in top header utility bar or PDP trade notice
+2. Observe URL redirection path
+3. Verify destination form loads without authentication roadblock.</v>
+      </c>
+      <c r="G21" t="str">
+        <v>CTA redirects directly to US Trade Application form (/trade-application or /customer/account/create) allowing public users to register.</v>
+      </c>
+      <c r="H21" t="str">
+        <v>PASS: Clicking 'Become a Trade Customer' routes cleanly to US registration page; guest registration workflow accessible.</v>
+      </c>
+      <c r="I21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J21" t="str">
+        <v>LOW (Verified Working)</v>
+      </c>
+      <c r="K21" t="str">
+        <v>comparison/COMPARISON_01_HEADER_GUEST_US_VS_AU.png</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-GW-PUB-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Search Autocomplete Popup</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Logged Out (Public Guest)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Verify Search Autocomplete Dropdown Price Masking for Public Guests</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Unauthenticated guest clicks search icon and enters product search query.</v>
+      </c>
+      <c r="F22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Click search icon in header
+2. Enter product query (e.g. 'sofa' or 'dining')
+3. Inspect search autocomplete suggestion dropdown
+4. Verify rendered product cards and pricing.</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Search suggestion items display product images, titles, and SKU without wholesale pricing or Add to Cart actions.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>PASS: Autocomplete popup renders product suggestions with zero price leakage and no cart buttons in guest state.</v>
+      </c>
+      <c r="I22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J22" t="str">
+        <v>LOW (Verified Working)</v>
+      </c>
+      <c r="K22" t="str">
+        <v>screenshots/02_US_PLP_GUEST_GRID.png</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>